--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02_ideal_cache.mp4</t>
+          <t>01_ideal_motion.mp4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.59</v>
+        <v>7.27</v>
       </c>
       <c r="D2" t="n">
-        <v>0.103</v>
+        <v>0.089</v>
       </c>
       <c r="E2" t="n">
-        <v>24.07</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>72.2098</v>
+        <v>0.4385</v>
       </c>
       <c r="G2" t="n">
-        <v>72.199</v>
+        <v>0.3268333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>111.9</v>
+        <v>104.7</v>
       </c>
       <c r="I2" t="n">
-        <v>185.4</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>02_ideal_cache.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.89</v>
+        <v>7.59</v>
       </c>
       <c r="D3" t="n">
-        <v>0.095</v>
+        <v>0.103</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2533</v>
+        <v>1.3205</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2533</v>
+        <v>1.3091</v>
       </c>
       <c r="H3" t="n">
-        <v>103.1</v>
+        <v>113.2</v>
       </c>
       <c r="I3" t="n">
-        <v>185.8</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.54</v>
+        <v>6.89</v>
       </c>
       <c r="D4" t="n">
-        <v>0.013</v>
+        <v>0.095</v>
       </c>
       <c r="E4" t="n">
-        <v>1.96</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>0.2533</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0.2533</v>
       </c>
       <c r="H4" t="n">
-        <v>102.8</v>
+        <v>108.3</v>
       </c>
       <c r="I4" t="n">
-        <v>240.7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25271.05</v>
+        <v>3.54</v>
       </c>
       <c r="D5" t="n">
-        <v>3.401</v>
+        <v>0.013</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>312.8</v>
+        <v>101.1</v>
       </c>
       <c r="I5" t="n">
-        <v>408.3</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08_break_moire.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,62 +630,293 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.08</v>
+        <v>25271.05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004</v>
+        <v>3.401</v>
       </c>
       <c r="E6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.875</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.875</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>114</v>
+        <v>318.9</v>
       </c>
       <c r="I6" t="n">
-        <v>198.7</v>
+        <v>387.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06_break_jitter.mp4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.3362</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.475</v>
+      </c>
+      <c r="H7" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07_break_fade.mp4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.3612</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.0974</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" t="n">
+        <v>172.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08_break_moire.mp4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>184.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09_scaling_ui.mp4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.849</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.138</v>
+      </c>
+      <c r="H10" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2frames.mp4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>36.56</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D11" t="n">
         <v>1.31</v>
       </c>
-      <c r="E7" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="F7" t="n">
-        <v>31.4136</v>
-      </c>
-      <c r="G7" t="n">
-        <v>31.4136</v>
-      </c>
-      <c r="H7" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>31.7</v>
+      <c r="E11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.6933</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.6933</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2frames_cd.mp4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>103.27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ball.mp4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.5161</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.374166666666667</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>countdown.mp4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2440.83</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14.734</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.91076666666667</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -695,7 +926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -705,7 +936,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -715,7 +946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -725,7 +956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -735,7 +966,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -745,7 +976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.27</v>
+        <v>12.7</v>
       </c>
       <c r="D2" t="n">
-        <v>0.089</v>
+        <v>0.156</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>144.41</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4385</v>
+        <v>359.6688</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3268333333333334</v>
+        <v>356.2198333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7</v>
+        <v>79.3</v>
       </c>
       <c r="I2" t="n">
-        <v>180.6</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.59</v>
+        <v>6.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.103</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.44</v>
+        <v>81.94</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3205</v>
+        <v>338.2523</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3091</v>
+        <v>338.2523</v>
       </c>
       <c r="H3" t="n">
-        <v>113.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>188.9</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="4">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.89</v>
+        <v>6.28</v>
       </c>
       <c r="D4" t="n">
-        <v>0.095</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2533</v>
+        <v>0.2287</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2533</v>
+        <v>0.2287</v>
       </c>
       <c r="H4" t="n">
-        <v>108.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>191</v>
+        <v>154.3</v>
       </c>
     </row>
     <row r="5">
@@ -603,19 +603,19 @@
         <v>0.013</v>
       </c>
       <c r="E5" t="n">
-        <v>1.96</v>
+        <v>4.46</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="H5" t="n">
-        <v>101.1</v>
+        <v>92.7</v>
       </c>
       <c r="I5" t="n">
-        <v>213.5</v>
+        <v>207.1</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>318.9</v>
+        <v>241.7</v>
       </c>
       <c r="I6" t="n">
-        <v>387.1</v>
+        <v>339.5</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.107</v>
+        <v>0.124</v>
       </c>
       <c r="E7" t="n">
-        <v>4.97</v>
+        <v>9.15</v>
       </c>
       <c r="F7" t="n">
-        <v>11.3362</v>
+        <v>38.5238</v>
       </c>
       <c r="G7" t="n">
-        <v>10.475</v>
+        <v>27.65263333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>83.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>173</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.68</v>
+        <v>15.82</v>
       </c>
       <c r="D8" t="n">
-        <v>0.132</v>
+        <v>0.216</v>
       </c>
       <c r="E8" t="n">
-        <v>3.48</v>
+        <v>203.99</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3612</v>
+        <v>480.8675</v>
       </c>
       <c r="G8" t="n">
-        <v>6.0974</v>
+        <v>477.3407</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>75.3</v>
       </c>
       <c r="I8" t="n">
-        <v>172.2</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>114.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>184.1</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.88</v>
+        <v>10.97</v>
       </c>
       <c r="D10" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="E10" t="n">
-        <v>4.7</v>
+        <v>4.01</v>
       </c>
       <c r="F10" t="n">
-        <v>11.849</v>
+        <v>8.1676</v>
       </c>
       <c r="G10" t="n">
-        <v>10.138</v>
+        <v>6.253966666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>75.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>157.5</v>
+        <v>136.8</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.56</v>
+        <v>36.55</v>
       </c>
       <c r="D11" t="n">
         <v>1.31</v>
       </c>
       <c r="E11" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6933</v>
+        <v>1.8265</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6933</v>
+        <v>1.8265</v>
       </c>
       <c r="H11" t="n">
-        <v>22.6</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="12">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103.27</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>1.515</v>
+        <v>1.511</v>
       </c>
       <c r="E12" t="n">
         <v>0.43</v>
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>23.3</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91.41</v>
+        <v>94.95</v>
       </c>
       <c r="D13" t="n">
-        <v>0.896</v>
+        <v>0.931</v>
       </c>
       <c r="E13" t="n">
-        <v>4.43</v>
+        <v>165.53</v>
       </c>
       <c r="F13" t="n">
-        <v>7.5161</v>
+        <v>1118.0206</v>
       </c>
       <c r="G13" t="n">
-        <v>7.374166666666667</v>
+        <v>807.6682999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I13" t="n">
-        <v>25.7</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2440.83</v>
+        <v>2407.37</v>
       </c>
       <c r="D14" t="n">
-        <v>1.607</v>
+        <v>1.585</v>
       </c>
       <c r="E14" t="n">
-        <v>6.43</v>
+        <v>60.98</v>
       </c>
       <c r="F14" t="n">
-        <v>14.734</v>
+        <v>129.9736</v>
       </c>
       <c r="G14" t="n">
-        <v>13.91076666666667</v>
+        <v>126.5604333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>21.8</v>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12.7</v>
+        <v>15.47</v>
       </c>
       <c r="D2" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>144.41</v>
+        <v>144.97</v>
       </c>
       <c r="F2" t="n">
-        <v>359.6688</v>
+        <v>360.32</v>
       </c>
       <c r="G2" t="n">
-        <v>356.2198333333333</v>
+        <v>351.90716</v>
       </c>
       <c r="H2" t="n">
-        <v>79.3</v>
+        <v>68</v>
       </c>
       <c r="I2" t="n">
-        <v>132</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="3">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.25</v>
+        <v>6.71</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="E3" t="n">
         <v>81.94</v>
@@ -546,10 +546,10 @@
         <v>338.2523</v>
       </c>
       <c r="H3" t="n">
-        <v>95.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="I3" t="n">
-        <v>158.5</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.2287</v>
       </c>
       <c r="H4" t="n">
-        <v>77.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I4" t="n">
-        <v>154.3</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="5">
@@ -609,13 +609,13 @@
         <v>225</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="H5" t="n">
-        <v>92.7</v>
+        <v>82</v>
       </c>
       <c r="I5" t="n">
-        <v>207.1</v>
+        <v>172.3</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>241.7</v>
+        <v>224.8</v>
       </c>
       <c r="I6" t="n">
-        <v>339.5</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.1</v>
+        <v>12.52</v>
       </c>
       <c r="D7" t="n">
-        <v>0.124</v>
+        <v>0.129</v>
       </c>
       <c r="E7" t="n">
-        <v>9.15</v>
+        <v>4.45</v>
       </c>
       <c r="F7" t="n">
-        <v>38.5238</v>
+        <v>24.5059</v>
       </c>
       <c r="G7" t="n">
-        <v>27.65263333333333</v>
+        <v>11.48928</v>
       </c>
       <c r="H7" t="n">
-        <v>67.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>145.2</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.82</v>
+        <v>19.07</v>
       </c>
       <c r="D8" t="n">
-        <v>0.216</v>
+        <v>0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>203.99</v>
+        <v>205.63</v>
       </c>
       <c r="F8" t="n">
-        <v>480.8675</v>
+        <v>480.1901</v>
       </c>
       <c r="G8" t="n">
-        <v>477.3407</v>
+        <v>473.7064999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>75.3</v>
+        <v>58.6</v>
       </c>
       <c r="I8" t="n">
-        <v>140.9</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="I9" t="n">
-        <v>159.3</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.97</v>
+        <v>12.04</v>
       </c>
       <c r="D10" t="n">
-        <v>0.107</v>
+        <v>0.117</v>
       </c>
       <c r="E10" t="n">
-        <v>4.01</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>8.1676</v>
+        <v>4.7256</v>
       </c>
       <c r="G10" t="n">
-        <v>6.253966666666666</v>
+        <v>3.1166</v>
       </c>
       <c r="H10" t="n">
-        <v>67.40000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="I10" t="n">
-        <v>136.8</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.55</v>
+        <v>36.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1.31</v>
+        <v>1.316</v>
       </c>
       <c r="E11" t="n">
-        <v>0.91</v>
+        <v>0.52</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8265</v>
+        <v>1.0395</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8265</v>
+        <v>1.0395</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I11" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="12">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>103.27</v>
       </c>
       <c r="D12" t="n">
-        <v>1.511</v>
+        <v>1.515</v>
       </c>
       <c r="E12" t="n">
         <v>0.43</v>
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="I12" t="n">
-        <v>17.2</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>94.95</v>
+        <v>108.41</v>
       </c>
       <c r="D13" t="n">
-        <v>0.931</v>
+        <v>1.063</v>
       </c>
       <c r="E13" t="n">
-        <v>165.53</v>
+        <v>168.53</v>
       </c>
       <c r="F13" t="n">
-        <v>1118.0206</v>
+        <v>1251.0857</v>
       </c>
       <c r="G13" t="n">
-        <v>807.6682999999999</v>
+        <v>809.32154</v>
       </c>
       <c r="H13" t="n">
-        <v>13.5</v>
+        <v>11.8</v>
       </c>
       <c r="I13" t="n">
-        <v>21.8</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2407.37</v>
+        <v>2531.46</v>
       </c>
       <c r="D14" t="n">
-        <v>1.585</v>
+        <v>1.666</v>
       </c>
       <c r="E14" t="n">
-        <v>60.98</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>129.9736</v>
+        <v>136.3826</v>
       </c>
       <c r="G14" t="n">
-        <v>126.5604333333333</v>
+        <v>133.71136</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.47</v>
+        <v>15.53</v>
       </c>
       <c r="D2" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="E2" t="n">
-        <v>144.97</v>
+        <v>145.1</v>
       </c>
       <c r="F2" t="n">
-        <v>360.32</v>
+        <v>360.4747</v>
       </c>
       <c r="G2" t="n">
-        <v>351.90716</v>
+        <v>352.03796</v>
       </c>
       <c r="H2" t="n">
-        <v>68</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>131.9</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v>338.2523</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3</v>
+        <v>88.3</v>
       </c>
       <c r="I3" t="n">
-        <v>144.2</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="4">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.28</v>
+        <v>6.36</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2287</v>
+        <v>0.2554</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2287</v>
+        <v>0.2554</v>
       </c>
       <c r="H4" t="n">
         <v>81.7</v>
       </c>
       <c r="I4" t="n">
-        <v>150.2</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>45</v>
       </c>
       <c r="H5" t="n">
-        <v>82</v>
+        <v>85.7</v>
       </c>
       <c r="I5" t="n">
-        <v>172.3</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>224.8</v>
+        <v>206.3</v>
       </c>
       <c r="I6" t="n">
-        <v>300.3</v>
+        <v>329.6</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.52</v>
+        <v>12.61</v>
       </c>
       <c r="D7" t="n">
         <v>0.129</v>
       </c>
       <c r="E7" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="F7" t="n">
-        <v>24.5059</v>
+        <v>37.0367</v>
       </c>
       <c r="G7" t="n">
-        <v>11.48928</v>
+        <v>15.15542</v>
       </c>
       <c r="H7" t="n">
-        <v>65.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>123.8</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="8">
@@ -711,10 +711,10 @@
         <v>473.7064999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="I8" t="n">
-        <v>116.7</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>82.7</v>
+        <v>91.5</v>
       </c>
       <c r="I9" t="n">
-        <v>146.2</v>
+        <v>156.4</v>
       </c>
     </row>
     <row r="10">
@@ -777,10 +777,10 @@
         <v>3.1166</v>
       </c>
       <c r="H10" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="I10" t="n">
-        <v>129.2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -810,10 +810,10 @@
         <v>1.0395</v>
       </c>
       <c r="H11" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="I11" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="12">
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="I12" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>108.41</v>
+        <v>105.58</v>
       </c>
       <c r="D13" t="n">
-        <v>1.063</v>
+        <v>1.035</v>
       </c>
       <c r="E13" t="n">
-        <v>168.53</v>
+        <v>169.03</v>
       </c>
       <c r="F13" t="n">
-        <v>1251.0857</v>
+        <v>1249.9009</v>
       </c>
       <c r="G13" t="n">
-        <v>809.32154</v>
+        <v>776.97578</v>
       </c>
       <c r="H13" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="I13" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2531.46</v>
+        <v>2553.08</v>
       </c>
       <c r="D14" t="n">
-        <v>1.666</v>
+        <v>1.68</v>
       </c>
       <c r="E14" t="n">
-        <v>67.40000000000001</v>
+        <v>72.06</v>
       </c>
       <c r="F14" t="n">
-        <v>136.3826</v>
+        <v>152.1406</v>
       </c>
       <c r="G14" t="n">
-        <v>133.71136</v>
+        <v>149.41084</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I14" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01_ideal_motion.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.53</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.191</v>
+        <v>0.014</v>
       </c>
       <c r="E2" t="n">
-        <v>145.1</v>
+        <v>0.23</v>
       </c>
       <c r="F2" t="n">
-        <v>360.4747</v>
+        <v>0.2554</v>
       </c>
       <c r="G2" t="n">
-        <v>352.03796</v>
+        <v>0.2554</v>
       </c>
       <c r="H2" t="n">
-        <v>71.90000000000001</v>
+        <v>107.3</v>
       </c>
       <c r="I2" t="n">
-        <v>129.4</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02_ideal_cache.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.71</v>
+        <v>0.34</v>
       </c>
       <c r="D3" t="n">
-        <v>0.091</v>
+        <v>0.001</v>
       </c>
       <c r="E3" t="n">
-        <v>81.94</v>
+        <v>1.96</v>
       </c>
       <c r="F3" t="n">
-        <v>338.2523</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>338.2523</v>
+        <v>5.4</v>
       </c>
       <c r="H3" t="n">
-        <v>88.3</v>
+        <v>90.3</v>
       </c>
       <c r="I3" t="n">
-        <v>152.8</v>
+        <v>229.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.36</v>
+        <v>25266.97</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08799999999999999</v>
+        <v>3.401</v>
       </c>
       <c r="E4" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2554</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2554</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>81.7</v>
+        <v>230.8</v>
       </c>
       <c r="I4" t="n">
-        <v>147.5</v>
+        <v>384.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>08_break_moire.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.54</v>
+        <v>0.26</v>
       </c>
       <c r="D5" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4.46</v>
+        <v>1.01</v>
       </c>
       <c r="F5" t="n">
-        <v>225</v>
+        <v>2.875</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>2.875</v>
       </c>
       <c r="H5" t="n">
-        <v>85.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>186.8</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>2frames.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,31 +630,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25271.05</v>
+        <v>36.67</v>
       </c>
       <c r="D6" t="n">
-        <v>3.401</v>
+        <v>1.315</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>23.56</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>47.1163</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>47.1163</v>
       </c>
       <c r="H6" t="n">
-        <v>206.3</v>
+        <v>17.1</v>
       </c>
       <c r="I6" t="n">
-        <v>329.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06_break_jitter.mp4</t>
+          <t>2frames_cd.mp4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,260 +663,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.61</v>
+        <v>103.46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129</v>
+        <v>1.518</v>
       </c>
       <c r="E7" t="n">
-        <v>4.67</v>
+        <v>0.43</v>
       </c>
       <c r="F7" t="n">
-        <v>37.0367</v>
+        <v>0.8646</v>
       </c>
       <c r="G7" t="n">
-        <v>15.15542</v>
+        <v>0.8646</v>
       </c>
       <c r="H7" t="n">
-        <v>64.09999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="I7" t="n">
-        <v>121.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07_break_fade.mp4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E8" t="n">
-        <v>205.63</v>
-      </c>
-      <c r="F8" t="n">
-        <v>480.1901</v>
-      </c>
-      <c r="G8" t="n">
-        <v>473.7064999999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>125.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08_break_moire.mp4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="H9" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>156.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09_scaling_ui.mp4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.7256</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.1166</v>
-      </c>
-      <c r="H10" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2frames.mp4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.0395</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.0395</v>
-      </c>
-      <c r="H11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2frames_cd.mp4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>103.27</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.515</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.8646</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.8646</v>
-      </c>
-      <c r="H12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ball.mp4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>105.58</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="E13" t="n">
-        <v>169.03</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1249.9009</v>
-      </c>
-      <c r="G13" t="n">
-        <v>776.97578</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>countdown.mp4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2553.08</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E14" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="F14" t="n">
-        <v>152.1406</v>
-      </c>
-      <c r="G14" t="n">
-        <v>149.41084</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>19</v>
+        <v>25.1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -926,7 +695,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -936,7 +705,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -946,7 +715,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -956,7 +725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -966,7 +735,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -976,7 +745,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>01_ideal_motion.mp4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2.96</v>
       </c>
       <c r="D2" t="n">
-        <v>0.014</v>
+        <v>0.036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.23</v>
+        <v>35.17</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2554</v>
+        <v>54.6556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2554</v>
+        <v>54.56698</v>
       </c>
       <c r="H2" t="n">
-        <v>107.3</v>
+        <v>113.2</v>
       </c>
       <c r="I2" t="n">
-        <v>192</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="E3" t="n">
-        <v>1.96</v>
+        <v>0.23</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>0.2554</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4</v>
+        <v>0.2554</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3</v>
+        <v>112.1</v>
       </c>
       <c r="I3" t="n">
-        <v>229.9</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25266.97</v>
+        <v>0.34</v>
       </c>
       <c r="D4" t="n">
-        <v>3.401</v>
+        <v>0.001</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>230.8</v>
+        <v>95.2</v>
       </c>
       <c r="I4" t="n">
-        <v>384.1</v>
+        <v>208.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08_break_moire.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.26</v>
+        <v>25266.97</v>
       </c>
       <c r="D5" t="n">
+        <v>3.401</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="F5" t="n">
-        <v>2.875</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.875</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>93.09999999999999</v>
+        <v>274</v>
       </c>
       <c r="I5" t="n">
-        <v>163.4</v>
+        <v>361.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2frames.mp4</t>
+          <t>07_break_fade.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,62 +630,128 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.67</v>
+        <v>4.51</v>
       </c>
       <c r="D6" t="n">
-        <v>1.315</v>
+        <v>0.062</v>
       </c>
       <c r="E6" t="n">
-        <v>23.56</v>
+        <v>14.16</v>
       </c>
       <c r="F6" t="n">
-        <v>47.1163</v>
+        <v>51.987</v>
       </c>
       <c r="G6" t="n">
-        <v>47.1163</v>
+        <v>48.49534</v>
       </c>
       <c r="H6" t="n">
-        <v>17.1</v>
+        <v>101.7</v>
       </c>
       <c r="I6" t="n">
-        <v>26.6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08_break_moire.mp4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="H7" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>196.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2frames.mp4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7516</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.7516</v>
+      </c>
+      <c r="H8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2frames_cd.mp4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>V6 Dynamic Boxing</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>103.46</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" t="n">
         <v>1.518</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E9" t="n">
         <v>0.43</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F9" t="n">
         <v>0.8646</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G9" t="n">
         <v>0.8646</v>
       </c>
-      <c r="H7" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>25.1</v>
+      <c r="H9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -695,7 +761,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -705,7 +771,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -715,7 +781,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -725,7 +791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -735,7 +801,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -745,7 +811,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="D2" t="n">
         <v>0.036</v>
       </c>
       <c r="E2" t="n">
-        <v>35.17</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>54.6556</v>
+        <v>0.4385</v>
       </c>
       <c r="G2" t="n">
-        <v>54.56698</v>
+        <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>113.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>189.8</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>02_ideal_cache.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3.83</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014</v>
+        <v>0.052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2554</v>
+        <v>1.3268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2554</v>
+        <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>112.1</v>
+        <v>90.2</v>
       </c>
       <c r="I3" t="n">
-        <v>188.1</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>1.96</v>
+        <v>0.23</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>0.2554</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4</v>
+        <v>0.2554</v>
       </c>
       <c r="H4" t="n">
-        <v>95.2</v>
+        <v>79.5</v>
       </c>
       <c r="I4" t="n">
-        <v>208.4</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25266.97</v>
+        <v>0.34</v>
       </c>
       <c r="D5" t="n">
-        <v>3.401</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>274</v>
+        <v>77.7</v>
       </c>
       <c r="I5" t="n">
-        <v>361.5</v>
+        <v>189.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07_break_fade.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,31 +630,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.51</v>
+        <v>25266.97</v>
       </c>
       <c r="D6" t="n">
-        <v>0.062</v>
+        <v>3.401</v>
       </c>
       <c r="E6" t="n">
-        <v>14.16</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>51.987</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>48.49534</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>101.7</v>
+        <v>244.4</v>
       </c>
       <c r="I6" t="n">
-        <v>182.4</v>
+        <v>325.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08_break_moire.mp4</t>
+          <t>06_break_jitter.mp4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.26</v>
+        <v>3.82</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>5.04</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875</v>
+        <v>12.3747</v>
       </c>
       <c r="G7" t="n">
-        <v>2.875</v>
+        <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>116.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>196.2</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2frames.mp4</t>
+          <t>07_break_fade.mp4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,62 +696,227 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36.66</v>
+        <v>4.54</v>
       </c>
       <c r="D8" t="n">
-        <v>1.314</v>
+        <v>0.062</v>
       </c>
       <c r="E8" t="n">
-        <v>0.88</v>
+        <v>3.96</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7516</v>
+        <v>8.5466</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7516</v>
+        <v>6.19236</v>
       </c>
       <c r="H8" t="n">
-        <v>27.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>29.6</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08_break_moire.mp4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>182.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09_scaling_ui.mp4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.022</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.24418</v>
+      </c>
+      <c r="H10" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>157.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2frames.mp4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7516</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.7516</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2frames_cd.mp4</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>103.46</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D12" t="n">
         <v>1.518</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E12" t="n">
         <v>0.43</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F12" t="n">
         <v>0.8646</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G12" t="n">
         <v>0.8646</v>
       </c>
-      <c r="H9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>29.2</v>
+      <c r="H12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ball.mp4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>76.4486</v>
+      </c>
+      <c r="G13" t="n">
+        <v>75.38412000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>countdown.mp4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1371.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.3722</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.12194</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -761,7 +926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -771,7 +936,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -781,7 +946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -791,7 +956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -801,7 +966,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -811,7 +976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="D2" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4385</v>
+        <v>0.67</v>
       </c>
       <c r="G2" t="n">
-        <v>0.30572</v>
+        <v>0.4906400000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>88.59999999999999</v>
+        <v>114.5</v>
       </c>
       <c r="I2" t="n">
-        <v>154.1</v>
+        <v>182.7</v>
       </c>
     </row>
     <row r="3">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="D3" t="n">
         <v>0.052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3268</v>
+        <v>5.1971</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3268</v>
+        <v>2.09414</v>
       </c>
       <c r="H3" t="n">
-        <v>90.2</v>
+        <v>110.5</v>
       </c>
       <c r="I3" t="n">
-        <v>146.5</v>
+        <v>183.9</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.2554</v>
       </c>
       <c r="H4" t="n">
-        <v>79.5</v>
+        <v>109.4</v>
       </c>
       <c r="I4" t="n">
-        <v>143.7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>77.7</v>
+        <v>89.7</v>
       </c>
       <c r="I5" t="n">
-        <v>189.1</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>244.4</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
-        <v>325.8</v>
+        <v>405.7</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="D7" t="n">
-        <v>0.039</v>
+        <v>0.034</v>
       </c>
       <c r="E7" t="n">
-        <v>5.04</v>
+        <v>7.58</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3747</v>
+        <v>44.4104</v>
       </c>
       <c r="G7" t="n">
-        <v>9.799000000000001</v>
+        <v>19.21902</v>
       </c>
       <c r="H7" t="n">
-        <v>69.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I7" t="n">
-        <v>143.7</v>
+        <v>185.6</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.54</v>
+        <v>4.87</v>
       </c>
       <c r="D8" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="E8" t="n">
-        <v>3.96</v>
+        <v>4.85</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5466</v>
+        <v>8.733700000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>6.19236</v>
+        <v>6.79936</v>
       </c>
       <c r="H8" t="n">
-        <v>77.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I8" t="n">
-        <v>142.4</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>94.5</v>
+        <v>115.5</v>
       </c>
       <c r="I9" t="n">
-        <v>182.2</v>
+        <v>190.4</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="D10" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="E10" t="n">
-        <v>4.73</v>
+        <v>4.54</v>
       </c>
       <c r="F10" t="n">
-        <v>11.022</v>
+        <v>39.2726</v>
       </c>
       <c r="G10" t="n">
-        <v>8.24418</v>
+        <v>18.87084</v>
       </c>
       <c r="H10" t="n">
-        <v>79.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>157.2</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.67</v>
+        <v>36.42</v>
       </c>
       <c r="D11" t="n">
-        <v>1.315</v>
+        <v>1.306</v>
       </c>
       <c r="E11" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7516</v>
+        <v>2.2241</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7516</v>
+        <v>2.2241</v>
       </c>
       <c r="H11" t="n">
-        <v>16.1</v>
+        <v>25.2</v>
       </c>
       <c r="I11" t="n">
-        <v>22.8</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="12">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103.46</v>
+        <v>103.39</v>
       </c>
       <c r="D12" t="n">
-        <v>1.518</v>
+        <v>1.517</v>
       </c>
       <c r="E12" t="n">
         <v>0.43</v>
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>14.9</v>
+        <v>20.4</v>
       </c>
       <c r="I12" t="n">
-        <v>20.6</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.01000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D13" t="n">
-        <v>0.706</v>
+        <v>0.649</v>
       </c>
       <c r="E13" t="n">
-        <v>27.7</v>
+        <v>27.49</v>
       </c>
       <c r="F13" t="n">
-        <v>76.4486</v>
+        <v>84.45359999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>75.38412000000001</v>
+        <v>81.77988000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1371.3</v>
+        <v>803.25</v>
       </c>
       <c r="D14" t="n">
-        <v>0.903</v>
+        <v>0.529</v>
       </c>
       <c r="E14" t="n">
-        <v>6.74</v>
+        <v>27.57</v>
       </c>
       <c r="F14" t="n">
-        <v>15.3722</v>
+        <v>80.3398</v>
       </c>
       <c r="G14" t="n">
-        <v>14.12194</v>
+        <v>76.64939999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>20.4</v>
+        <v>23.3</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="D2" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>0.67</v>
+        <v>0.4375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4906400000000001</v>
+        <v>0.30348</v>
       </c>
       <c r="H2" t="n">
-        <v>114.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>182.7</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="3">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="D3" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="E3" t="n">
         <v>0.53</v>
@@ -546,10 +546,10 @@
         <v>2.09414</v>
       </c>
       <c r="H3" t="n">
-        <v>110.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>183.9</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.2554</v>
       </c>
       <c r="H4" t="n">
-        <v>109.4</v>
+        <v>84</v>
       </c>
       <c r="I4" t="n">
-        <v>200</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>89.7</v>
+        <v>82.8</v>
       </c>
       <c r="I5" t="n">
-        <v>241.3</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>270</v>
+        <v>240.6</v>
       </c>
       <c r="I6" t="n">
-        <v>405.7</v>
+        <v>358.6</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="D7" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="E7" t="n">
-        <v>7.58</v>
+        <v>11.02</v>
       </c>
       <c r="F7" t="n">
-        <v>44.4104</v>
+        <v>52.0825</v>
       </c>
       <c r="G7" t="n">
-        <v>19.21902</v>
+        <v>33.14971999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>87.8</v>
+        <v>75</v>
       </c>
       <c r="I7" t="n">
-        <v>185.6</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.87</v>
+        <v>4.68</v>
       </c>
       <c r="D8" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="E8" t="n">
-        <v>4.85</v>
+        <v>5.31</v>
       </c>
       <c r="F8" t="n">
-        <v>8.733700000000001</v>
+        <v>14.0153</v>
       </c>
       <c r="G8" t="n">
-        <v>6.79936</v>
+        <v>7.929780000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>91.2</v>
+        <v>62.4</v>
       </c>
       <c r="I8" t="n">
-        <v>191.7</v>
+        <v>131.4</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>115.5</v>
+        <v>90.2</v>
       </c>
       <c r="I9" t="n">
-        <v>190.4</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="D10" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="E10" t="n">
-        <v>4.54</v>
+        <v>4.26</v>
       </c>
       <c r="F10" t="n">
-        <v>39.2726</v>
+        <v>30.0564</v>
       </c>
       <c r="G10" t="n">
-        <v>18.87084</v>
+        <v>18.5607</v>
       </c>
       <c r="H10" t="n">
-        <v>75.90000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="I10" t="n">
-        <v>177.5</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.42</v>
+        <v>36.38</v>
       </c>
       <c r="D11" t="n">
-        <v>1.306</v>
+        <v>1.304</v>
       </c>
       <c r="E11" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2241</v>
+        <v>1.8797</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2241</v>
+        <v>1.8797</v>
       </c>
       <c r="H11" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="I11" t="n">
-        <v>31.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="12">
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>20.4</v>
+        <v>16.2</v>
       </c>
       <c r="I12" t="n">
-        <v>27.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>66.22</v>
+        <v>63.17</v>
       </c>
       <c r="D13" t="n">
-        <v>0.649</v>
+        <v>0.619</v>
       </c>
       <c r="E13" t="n">
-        <v>27.49</v>
+        <v>28.73</v>
       </c>
       <c r="F13" t="n">
-        <v>84.45359999999999</v>
+        <v>114.1283</v>
       </c>
       <c r="G13" t="n">
-        <v>81.77988000000001</v>
+        <v>104.60574</v>
       </c>
       <c r="H13" t="n">
-        <v>15.3</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>803.25</v>
+        <v>644.54</v>
       </c>
       <c r="D14" t="n">
-        <v>0.529</v>
+        <v>0.424</v>
       </c>
       <c r="E14" t="n">
-        <v>27.57</v>
+        <v>19.8</v>
       </c>
       <c r="F14" t="n">
-        <v>80.3398</v>
+        <v>63.9843</v>
       </c>
       <c r="G14" t="n">
-        <v>76.64939999999999</v>
+        <v>60.75634</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="D2" t="n">
         <v>0.036</v>
@@ -507,16 +507,16 @@
         <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4375</v>
+        <v>0.4385</v>
       </c>
       <c r="G2" t="n">
-        <v>0.30348</v>
+        <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>81.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="I2" t="n">
-        <v>149.1</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="3">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="D3" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1971</v>
+        <v>1.3268</v>
       </c>
       <c r="G3" t="n">
-        <v>2.09414</v>
+        <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>83.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>138</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.2554</v>
       </c>
       <c r="H4" t="n">
-        <v>84</v>
+        <v>62.8</v>
       </c>
       <c r="I4" t="n">
-        <v>150.1</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>82.8</v>
+        <v>79.7</v>
       </c>
       <c r="I5" t="n">
-        <v>178.7</v>
+        <v>190.5</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>240.6</v>
+        <v>229.6</v>
       </c>
       <c r="I6" t="n">
-        <v>358.6</v>
+        <v>316.7</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.37</v>
+        <v>3.82</v>
       </c>
       <c r="D7" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="E7" t="n">
-        <v>11.02</v>
+        <v>5.04</v>
       </c>
       <c r="F7" t="n">
-        <v>52.0825</v>
+        <v>12.3747</v>
       </c>
       <c r="G7" t="n">
-        <v>33.14971999999999</v>
+        <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
+        <v>62.6</v>
       </c>
       <c r="I7" t="n">
-        <v>125.7</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.68</v>
+        <v>4.54</v>
       </c>
       <c r="D8" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="E8" t="n">
-        <v>5.31</v>
+        <v>3.96</v>
       </c>
       <c r="F8" t="n">
-        <v>14.0153</v>
+        <v>8.5466</v>
       </c>
       <c r="G8" t="n">
-        <v>7.929780000000001</v>
+        <v>6.19236</v>
       </c>
       <c r="H8" t="n">
-        <v>62.4</v>
+        <v>77.2</v>
       </c>
       <c r="I8" t="n">
-        <v>131.4</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>90.2</v>
+        <v>86.8</v>
       </c>
       <c r="I9" t="n">
-        <v>143.2</v>
+        <v>158.9</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.44</v>
+        <v>3.68</v>
       </c>
       <c r="D10" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="E10" t="n">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="F10" t="n">
-        <v>30.0564</v>
+        <v>11.022</v>
       </c>
       <c r="G10" t="n">
-        <v>18.5607</v>
+        <v>8.2713</v>
       </c>
       <c r="H10" t="n">
-        <v>60.5</v>
+        <v>63.7</v>
       </c>
       <c r="I10" t="n">
-        <v>134.5</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.38</v>
+        <v>36.67</v>
       </c>
       <c r="D11" t="n">
-        <v>1.304</v>
+        <v>1.315</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8797</v>
+        <v>1.7516</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8797</v>
+        <v>1.7516</v>
       </c>
       <c r="H11" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="I11" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="12">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103.39</v>
+        <v>103.46</v>
       </c>
       <c r="D12" t="n">
-        <v>1.517</v>
+        <v>1.518</v>
       </c>
       <c r="E12" t="n">
         <v>0.43</v>
@@ -843,10 +843,10 @@
         <v>0.8646</v>
       </c>
       <c r="H12" t="n">
-        <v>16.2</v>
+        <v>12.7</v>
       </c>
       <c r="I12" t="n">
-        <v>21.9</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="13">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>63.17</v>
+        <v>72.12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.619</v>
+        <v>0.707</v>
       </c>
       <c r="E13" t="n">
-        <v>28.73</v>
+        <v>4.52</v>
       </c>
       <c r="F13" t="n">
-        <v>114.1283</v>
+        <v>8.318199999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>104.60574</v>
+        <v>7.31036</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="I13" t="n">
-        <v>26.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14">
@@ -894,25 +894,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>644.54</v>
+        <v>1368.01</v>
       </c>
       <c r="D14" t="n">
-        <v>0.424</v>
+        <v>0.9</v>
       </c>
       <c r="E14" t="n">
-        <v>19.8</v>
+        <v>6.55</v>
       </c>
       <c r="F14" t="n">
-        <v>63.9843</v>
+        <v>15.5043</v>
       </c>
       <c r="G14" t="n">
-        <v>60.75634</v>
+        <v>14.12994</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>24.2</v>
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.95</v>
+        <v>7.25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.036</v>
+        <v>0.089</v>
       </c>
       <c r="E2" t="n">
         <v>0.22</v>
@@ -513,10 +513,10 @@
         <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>71</v>
+        <v>84.8</v>
       </c>
       <c r="I2" t="n">
-        <v>82.5</v>
+        <v>154.7</v>
       </c>
     </row>
     <row r="3">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.83</v>
+        <v>7.39</v>
       </c>
       <c r="D3" t="n">
-        <v>0.052</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -546,10 +546,10 @@
         <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>66.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>121.2</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="4">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3.54</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014</v>
+        <v>0.049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2554</v>
+        <v>0.1001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2554</v>
+        <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>62.8</v>
+        <v>91.2</v>
       </c>
       <c r="I4" t="n">
-        <v>166.6</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="5">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.34</v>
+        <v>3.54</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="E5" t="n">
         <v>1.96</v>
@@ -612,10 +612,10 @@
         <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>79.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>190.5</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="6">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25266.97</v>
+        <v>25271.05</v>
       </c>
       <c r="D6" t="n">
         <v>3.401</v>
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>229.6</v>
+        <v>248.9</v>
       </c>
       <c r="I6" t="n">
-        <v>316.7</v>
+        <v>334.3</v>
       </c>
     </row>
     <row r="7">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.82</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.039</v>
+        <v>0.102</v>
       </c>
       <c r="E7" t="n">
         <v>5.04</v>
@@ -678,10 +678,10 @@
         <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>62.6</v>
+        <v>61.1</v>
       </c>
       <c r="I7" t="n">
-        <v>134.2</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.062</v>
+        <v>0.134</v>
       </c>
       <c r="E8" t="n">
         <v>3.96</v>
@@ -711,10 +711,10 @@
         <v>6.19236</v>
       </c>
       <c r="H8" t="n">
-        <v>77.2</v>
+        <v>73.7</v>
       </c>
       <c r="I8" t="n">
-        <v>164.2</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="9">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.26</v>
+        <v>2.78</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E9" t="n">
         <v>1.01</v>
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>86.8</v>
+        <v>85.5</v>
       </c>
       <c r="I9" t="n">
-        <v>158.9</v>
+        <v>171.9</v>
       </c>
     </row>
     <row r="10">
@@ -762,31 +762,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.68</v>
+        <v>10.27</v>
       </c>
       <c r="D10" t="n">
-        <v>0.036</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>4.74</v>
+        <v>4.55</v>
       </c>
       <c r="F10" t="n">
-        <v>11.022</v>
+        <v>11.3313</v>
       </c>
       <c r="G10" t="n">
-        <v>8.2713</v>
+        <v>8.058059999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>63.7</v>
+        <v>71.7</v>
       </c>
       <c r="I10" t="n">
-        <v>134.6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2frames.mp4</t>
+          <t>ball.mp4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.67</v>
+        <v>84.05</v>
       </c>
       <c r="D11" t="n">
-        <v>1.315</v>
+        <v>0.824</v>
       </c>
       <c r="E11" t="n">
-        <v>0.88</v>
+        <v>4.57</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7516</v>
+        <v>8.348800000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7516</v>
+        <v>7.911280000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>22.4</v>
+        <v>13.7</v>
       </c>
       <c r="I11" t="n">
-        <v>23.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2frames_cd.mp4</t>
+          <t>countdown.mp4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,95 +828,29 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103.46</v>
+        <v>1955.39</v>
       </c>
       <c r="D12" t="n">
-        <v>1.518</v>
+        <v>1.287</v>
       </c>
       <c r="E12" t="n">
-        <v>0.43</v>
+        <v>6.64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8646</v>
+        <v>15.5254</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8646</v>
+        <v>14.43464</v>
       </c>
       <c r="H12" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ball.mp4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8.318199999999999</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.31036</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>countdown.mp4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1368.01</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>15.5043</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14.12994</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12.9</v>
+        <v>21.9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -926,7 +860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -936,7 +870,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -946,7 +880,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -956,7 +890,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -966,7 +900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -976,7 +910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.25</v>
+        <v>7.08</v>
       </c>
       <c r="D2" t="n">
-        <v>0.089</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>0.22</v>
@@ -513,10 +513,10 @@
         <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>84.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>154.7</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>148.4</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>91.2</v>
+        <v>101.6</v>
       </c>
       <c r="I4" t="n">
-        <v>165.7</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="5">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="D5" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="E5" t="n">
-        <v>1.96</v>
+        <v>7.42</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>13.2</v>
       </c>
       <c r="H5" t="n">
-        <v>76.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I5" t="n">
-        <v>209.9</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>248.9</v>
+        <v>224.5</v>
       </c>
       <c r="I6" t="n">
-        <v>334.3</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>0.102</v>
@@ -678,10 +678,10 @@
         <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>61.1</v>
+        <v>68.8</v>
       </c>
       <c r="I7" t="n">
-        <v>149</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="D8" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="E8" t="n">
         <v>3.96</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5466</v>
+        <v>8.5473</v>
       </c>
       <c r="G8" t="n">
         <v>6.19236</v>
       </c>
       <c r="H8" t="n">
-        <v>73.7</v>
+        <v>70.7</v>
       </c>
       <c r="I8" t="n">
-        <v>125.6</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>171.9</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="10">
@@ -777,10 +777,10 @@
         <v>8.058059999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>71.7</v>
+        <v>52</v>
       </c>
       <c r="I10" t="n">
-        <v>160</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84.05</v>
+        <v>88.05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.824</v>
+        <v>0.863</v>
       </c>
       <c r="E11" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="F11" t="n">
-        <v>8.348800000000001</v>
+        <v>8.3316</v>
       </c>
       <c r="G11" t="n">
-        <v>7.911280000000001</v>
+        <v>7.568659999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>13.7</v>
+        <v>11.5</v>
       </c>
       <c r="I11" t="n">
-        <v>24.7</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="12">
@@ -828,25 +828,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1955.39</v>
+        <v>1950.57</v>
       </c>
       <c r="D12" t="n">
-        <v>1.287</v>
+        <v>1.284</v>
       </c>
       <c r="E12" t="n">
-        <v>6.64</v>
+        <v>6.45</v>
       </c>
       <c r="F12" t="n">
-        <v>15.5254</v>
+        <v>15.5444</v>
       </c>
       <c r="G12" t="n">
-        <v>14.43464</v>
+        <v>14.28832</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -513,10 +513,10 @@
         <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>85.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I2" t="n">
-        <v>156.5</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>84.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="I3" t="n">
-        <v>144.5</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>101.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>152.1</v>
+        <v>160.9</v>
       </c>
     </row>
     <row r="5">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="D5" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="E5" t="n">
-        <v>7.42</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>92.5</v>
+        <v>71.3</v>
       </c>
       <c r="I5" t="n">
-        <v>183.6</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>224.5</v>
+        <v>258.6</v>
       </c>
       <c r="I6" t="n">
-        <v>324.9</v>
+        <v>342.3</v>
       </c>
     </row>
     <row r="7">
@@ -678,10 +678,10 @@
         <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>68.8</v>
+        <v>66.2</v>
       </c>
       <c r="I7" t="n">
-        <v>112.2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
@@ -702,19 +702,19 @@
         <v>0.133</v>
       </c>
       <c r="E8" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5473</v>
+        <v>8.5341</v>
       </c>
       <c r="G8" t="n">
-        <v>6.19236</v>
+        <v>6.19336</v>
       </c>
       <c r="H8" t="n">
-        <v>70.7</v>
+        <v>76.7</v>
       </c>
       <c r="I8" t="n">
-        <v>130.9</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>107.3</v>
       </c>
       <c r="I9" t="n">
-        <v>129.5</v>
+        <v>199.4</v>
       </c>
     </row>
     <row r="10">
@@ -777,10 +777,10 @@
         <v>8.058059999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>52</v>
+        <v>75.2</v>
       </c>
       <c r="I10" t="n">
-        <v>110.7</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>88.05</v>
+        <v>86.59</v>
       </c>
       <c r="D11" t="n">
-        <v>0.863</v>
+        <v>0.849</v>
       </c>
       <c r="E11" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="F11" t="n">
-        <v>8.3316</v>
+        <v>8.458</v>
       </c>
       <c r="G11" t="n">
-        <v>7.568659999999999</v>
+        <v>7.11382</v>
       </c>
       <c r="H11" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="I11" t="n">
-        <v>23.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="12">
@@ -828,25 +828,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1950.57</v>
+        <v>1952.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1.284</v>
+        <v>1.285</v>
       </c>
       <c r="E12" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="n">
-        <v>15.5444</v>
+        <v>15.1434</v>
       </c>
       <c r="G12" t="n">
-        <v>14.28832</v>
+        <v>14.4033</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01_ideal_motion.mp4</t>
+          <t>02_ideal_cache.mp4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.08</v>
+        <v>7.39</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4385</v>
+        <v>1.3268</v>
       </c>
       <c r="G2" t="n">
-        <v>0.30572</v>
+        <v>1.3268</v>
       </c>
       <c r="H2" t="n">
-        <v>76.5</v>
+        <v>81.2</v>
       </c>
       <c r="I2" t="n">
-        <v>163.2</v>
+        <v>141.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02_ideal_cache.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.39</v>
+        <v>3.54</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.45</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3268</v>
+        <v>0.1001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3268</v>
+        <v>0.1001</v>
       </c>
       <c r="H3" t="n">
-        <v>82.7</v>
+        <v>88.7</v>
       </c>
       <c r="I3" t="n">
-        <v>132.2</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.54</v>
+        <v>3.91</v>
       </c>
       <c r="D4" t="n">
-        <v>0.049</v>
+        <v>0.015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1001</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1001</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>91.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="I4" t="n">
-        <v>160.9</v>
+        <v>183.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.91</v>
+        <v>25271.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.015</v>
+        <v>3.401</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>71.3</v>
+        <v>232.4</v>
       </c>
       <c r="I5" t="n">
-        <v>178.7</v>
+        <v>359.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>07_break_fade.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,31 +630,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25271.05</v>
+        <v>9.77</v>
       </c>
       <c r="D6" t="n">
-        <v>3.401</v>
+        <v>0.133</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8.5341</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6.19336</v>
       </c>
       <c r="H6" t="n">
-        <v>258.6</v>
+        <v>82</v>
       </c>
       <c r="I6" t="n">
-        <v>342.3</v>
+        <v>190.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06_break_jitter.mp4</t>
+          <t>08_break_moire.mp4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.960000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="D7" t="n">
-        <v>0.102</v>
+        <v>0.004</v>
       </c>
       <c r="E7" t="n">
-        <v>5.04</v>
+        <v>1.01</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3747</v>
+        <v>2.875</v>
       </c>
       <c r="G7" t="n">
-        <v>9.799000000000001</v>
+        <v>2.875</v>
       </c>
       <c r="H7" t="n">
-        <v>66.2</v>
+        <v>108.3</v>
       </c>
       <c r="I7" t="n">
-        <v>146</v>
+        <v>188.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07_break_fade.mp4</t>
+          <t>ball.mp4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,161 +696,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.77</v>
+        <v>86.59</v>
       </c>
       <c r="D8" t="n">
-        <v>0.133</v>
+        <v>0.849</v>
       </c>
       <c r="E8" t="n">
-        <v>3.97</v>
+        <v>4.52</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5341</v>
+        <v>8.458</v>
       </c>
       <c r="G8" t="n">
-        <v>6.19336</v>
+        <v>7.11382</v>
       </c>
       <c r="H8" t="n">
-        <v>76.7</v>
+        <v>11.2</v>
       </c>
       <c r="I8" t="n">
-        <v>176.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08_break_moire.mp4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="H9" t="n">
-        <v>107.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>199.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09_scaling_ui.mp4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11.3313</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.058059999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ball.mp4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>86.59</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.11382</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>26.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>countdown.mp4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1952.87</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="E12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>15.1434</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14.4033</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>22.3</v>
+        <v>24.6</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -860,7 +728,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -870,7 +738,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -880,7 +748,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -890,7 +758,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -900,7 +768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -910,7 +778,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02_ideal_cache.mp4</t>
+          <t>01_ideal_motion.mp4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,31 +498,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.39</v>
+        <v>7.06</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.45</v>
+        <v>1.59</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3268</v>
+        <v>21.6932</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3268</v>
+        <v>18.97034</v>
       </c>
       <c r="H2" t="n">
-        <v>81.2</v>
+        <v>78.8</v>
       </c>
       <c r="I2" t="n">
-        <v>141.1</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03_ideal_palette.mp4</t>
+          <t>02_ideal_cache.mp4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,31 +531,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.54</v>
+        <v>7.39</v>
       </c>
       <c r="D3" t="n">
-        <v>0.049</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1001</v>
+        <v>1.3268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1001</v>
+        <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>88.7</v>
+        <v>100.2</v>
       </c>
       <c r="I3" t="n">
-        <v>120.8</v>
+        <v>183.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04_ideal_baseline.mp4</t>
+          <t>03_ideal_palette.mp4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,31 +564,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.91</v>
+        <v>3.54</v>
       </c>
       <c r="D4" t="n">
-        <v>0.015</v>
+        <v>0.049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.1001</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>69.7</v>
+        <v>113</v>
       </c>
       <c r="I4" t="n">
-        <v>183.1</v>
+        <v>140.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05_break_entropy.mp4</t>
+          <t>04_ideal_baseline.mp4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25271.05</v>
+        <v>3.91</v>
       </c>
       <c r="D5" t="n">
-        <v>3.401</v>
+        <v>0.015</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>232.4</v>
+        <v>69.3</v>
       </c>
       <c r="I5" t="n">
-        <v>359.9</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07_break_fade.mp4</t>
+          <t>05_break_entropy.mp4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,31 +630,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.77</v>
+        <v>25271.05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.133</v>
+        <v>3.401</v>
       </c>
       <c r="E6" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>8.5341</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.19336</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>82</v>
+        <v>232.8</v>
       </c>
       <c r="I6" t="n">
-        <v>190.3</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08_break_moire.mp4</t>
+          <t>06_break_jitter.mp4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,62 +663,194 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.78</v>
+        <v>10.02</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004</v>
+        <v>0.103</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>5.12</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875</v>
+        <v>13.9802</v>
       </c>
       <c r="G7" t="n">
-        <v>2.875</v>
+        <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>108.3</v>
+        <v>53.6</v>
       </c>
       <c r="I7" t="n">
-        <v>188.3</v>
+        <v>139.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07_break_fade.mp4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.5341</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.19336</v>
+      </c>
+      <c r="H8" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>138.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08_break_moire.mp4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" t="n">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09_scaling_ui.mp4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.7529</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.84398</v>
+      </c>
+      <c r="H10" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>129.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>ball.mp4</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>86.59</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D11" t="n">
         <v>0.849</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
         <v>4.52</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F11" t="n">
         <v>8.458</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G11" t="n">
         <v>7.11382</v>
       </c>
-      <c r="H8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>24.6</v>
+      <c r="H11" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>countdown.mp4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1938.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.2035</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.44252</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>17.8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -728,7 +860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -738,7 +870,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -748,7 +880,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -758,7 +890,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -768,7 +900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -778,7 +910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -498,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.06</v>
+        <v>6.87</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1.59</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>21.6932</v>
+        <v>0.4385</v>
       </c>
       <c r="G2" t="n">
-        <v>18.97034</v>
+        <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>78.8</v>
+        <v>79.2</v>
       </c>
       <c r="I2" t="n">
-        <v>161</v>
+        <v>156.1</v>
       </c>
     </row>
     <row r="3">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.39</v>
+        <v>7.28</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -546,10 +546,10 @@
         <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>100.2</v>
+        <v>72.5</v>
       </c>
       <c r="I3" t="n">
-        <v>183.1</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="I4" t="n">
-        <v>140.1</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>69.3</v>
+        <v>59.2</v>
       </c>
       <c r="I5" t="n">
-        <v>177.6</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>232.8</v>
+        <v>210.7</v>
       </c>
       <c r="I6" t="n">
-        <v>326</v>
+        <v>299.9</v>
       </c>
     </row>
     <row r="7">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.02</v>
+        <v>9.44</v>
       </c>
       <c r="D7" t="n">
-        <v>0.103</v>
+        <v>0.097</v>
       </c>
       <c r="E7" t="n">
         <v>5.12</v>
@@ -678,10 +678,10 @@
         <v>9.799000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>53.6</v>
+        <v>53.9</v>
       </c>
       <c r="I7" t="n">
-        <v>139.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="8">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.77</v>
+        <v>9.52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
         <v>3.97</v>
@@ -711,10 +711,10 @@
         <v>6.19336</v>
       </c>
       <c r="H8" t="n">
-        <v>66.7</v>
+        <v>71.3</v>
       </c>
       <c r="I8" t="n">
-        <v>138.7</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>95.3</v>
       </c>
       <c r="I9" t="n">
-        <v>99.5</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.36</v>
+        <v>9.66</v>
       </c>
       <c r="D10" t="n">
-        <v>0.101</v>
+        <v>0.094</v>
       </c>
       <c r="E10" t="n">
-        <v>3.79</v>
+        <v>4.57</v>
       </c>
       <c r="F10" t="n">
-        <v>8.7529</v>
+        <v>10.4479</v>
       </c>
       <c r="G10" t="n">
-        <v>6.84398</v>
+        <v>7.54028</v>
       </c>
       <c r="H10" t="n">
-        <v>49.7</v>
+        <v>55.2</v>
       </c>
       <c r="I10" t="n">
-        <v>129.1</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="11">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86.59</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.849</v>
+        <v>0.827</v>
       </c>
       <c r="E11" t="n">
         <v>4.52</v>
@@ -810,47 +810,14 @@
         <v>7.11382</v>
       </c>
       <c r="H11" t="n">
-        <v>12.7</v>
+        <v>10.1</v>
       </c>
       <c r="I11" t="n">
-        <v>21.9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>countdown.mp4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>V6 Dynamic Boxing</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1938.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.276</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16.2035</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14.44252</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -860,7 +827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -870,7 +837,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -880,7 +847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -890,7 +857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -900,7 +867,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -910,7 +877,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,10 +513,10 @@
         <v>0.30572</v>
       </c>
       <c r="H2" t="n">
-        <v>79.2</v>
+        <v>84.3</v>
       </c>
       <c r="I2" t="n">
-        <v>156.1</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v>1.3268</v>
       </c>
       <c r="H3" t="n">
-        <v>72.5</v>
+        <v>78.2</v>
       </c>
       <c r="I3" t="n">
-        <v>108.3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +579,10 @@
         <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="I4" t="n">
-        <v>129.8</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="5">
@@ -612,10 +612,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>59.2</v>
+        <v>58.8</v>
       </c>
       <c r="I5" t="n">
-        <v>153.8</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>210.7</v>
+        <v>193.5</v>
       </c>
       <c r="I6" t="n">
-        <v>299.9</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.44</v>
+        <v>7.77</v>
       </c>
       <c r="D7" t="n">
-        <v>0.097</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>13.9802</v>
+        <v>13.3748</v>
       </c>
       <c r="G7" t="n">
-        <v>9.799000000000001</v>
+        <v>9.266999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>53.9</v>
+        <v>51.8</v>
       </c>
       <c r="I7" t="n">
-        <v>135.6</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="8">
@@ -696,25 +696,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.52</v>
+        <v>9.58</v>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="E8" t="n">
-        <v>3.97</v>
+        <v>3.88</v>
       </c>
       <c r="F8" t="n">
         <v>8.5341</v>
       </c>
       <c r="G8" t="n">
-        <v>6.19336</v>
+        <v>6.20472</v>
       </c>
       <c r="H8" t="n">
-        <v>71.3</v>
+        <v>61</v>
       </c>
       <c r="I8" t="n">
-        <v>166.2</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="9">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>95.3</v>
+        <v>76.7</v>
       </c>
       <c r="I9" t="n">
-        <v>175.4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.66</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="E10" t="n">
-        <v>4.57</v>
+        <v>23.37</v>
       </c>
       <c r="F10" t="n">
-        <v>10.4479</v>
+        <v>192.0872</v>
       </c>
       <c r="G10" t="n">
-        <v>7.54028</v>
+        <v>172.77168</v>
       </c>
       <c r="H10" t="n">
-        <v>55.2</v>
+        <v>47.6</v>
       </c>
       <c r="I10" t="n">
-        <v>142.4</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="11">
@@ -795,29 +795,62 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84.31999999999999</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.827</v>
+        <v>0.74</v>
       </c>
       <c r="E11" t="n">
-        <v>4.52</v>
+        <v>4.66</v>
       </c>
       <c r="F11" t="n">
-        <v>8.458</v>
+        <v>8.3729</v>
       </c>
       <c r="G11" t="n">
-        <v>7.11382</v>
+        <v>7.535199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>16.8</v>
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>countdown.mp4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V6 Dynamic Boxing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1834.09</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.3372</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.71752</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -827,7 +860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -837,7 +870,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -847,7 +880,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -857,7 +890,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -867,7 +900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -877,7 +910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/compression_report.xlsx
+++ b/compression_report.xlsx
@@ -494,29 +494,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.87</v>
+        <v>6.97</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.59</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4385</v>
+        <v>0.9736</v>
       </c>
       <c r="G2" t="n">
-        <v>0.30572</v>
+        <v>0.8840199999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>84.3</v>
+        <v>87.5</v>
       </c>
       <c r="I2" t="n">
-        <v>159</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="3">
@@ -527,29 +527,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.28</v>
+        <v>7.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="E3" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3268</v>
+        <v>1.3205</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3268</v>
+        <v>1.16284</v>
       </c>
       <c r="H3" t="n">
-        <v>78.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>116</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -579,10 +579,10 @@
         <v>0.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>65.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>134.9</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -612,10 +612,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>58.8</v>
+        <v>56.4</v>
       </c>
       <c r="I5" t="n">
-        <v>146.4</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="6">
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>193.5</v>
+        <v>200.5</v>
       </c>
       <c r="I6" t="n">
-        <v>279</v>
+        <v>292.3</v>
       </c>
     </row>
     <row r="7">
@@ -659,29 +659,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="F7" t="n">
-        <v>13.3748</v>
+        <v>14.4948</v>
       </c>
       <c r="G7" t="n">
-        <v>9.266999999999999</v>
+        <v>11.52988</v>
       </c>
       <c r="H7" t="n">
-        <v>51.8</v>
+        <v>56.5</v>
       </c>
       <c r="I7" t="n">
-        <v>134.1</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="8">
@@ -692,7 +692,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -702,19 +702,19 @@
         <v>0.131</v>
       </c>
       <c r="E8" t="n">
-        <v>3.88</v>
+        <v>2.93</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5341</v>
+        <v>8.536300000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>6.20472</v>
+        <v>6.557599999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" t="n">
-        <v>129.8</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -725,7 +725,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -744,10 +744,10 @@
         <v>2.875</v>
       </c>
       <c r="H9" t="n">
-        <v>76.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>138</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="10">
@@ -758,29 +758,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.390000000000001</v>
+        <v>12.59</v>
       </c>
       <c r="D10" t="n">
-        <v>0.091</v>
+        <v>0.122</v>
       </c>
       <c r="E10" t="n">
-        <v>23.37</v>
+        <v>22.28</v>
       </c>
       <c r="F10" t="n">
-        <v>192.0872</v>
+        <v>61.0664</v>
       </c>
       <c r="G10" t="n">
-        <v>172.77168</v>
+        <v>48.99088</v>
       </c>
       <c r="H10" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="I10" t="n">
-        <v>127.5</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="11">
@@ -791,29 +791,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.43000000000001</v>
+        <v>153.69</v>
       </c>
       <c r="D11" t="n">
-        <v>0.74</v>
+        <v>1.507</v>
       </c>
       <c r="E11" t="n">
-        <v>4.66</v>
+        <v>3.63</v>
       </c>
       <c r="F11" t="n">
-        <v>8.3729</v>
+        <v>7.5078</v>
       </c>
       <c r="G11" t="n">
-        <v>7.535199999999999</v>
+        <v>6.225779999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I11" t="n">
-        <v>21.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="12">
@@ -824,29 +824,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V6 Dynamic Boxing</t>
+          <t>V7 Dynamic Boxing</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1834.09</v>
+        <v>2064.92</v>
       </c>
       <c r="D12" t="n">
-        <v>1.207</v>
+        <v>1.359</v>
       </c>
       <c r="E12" t="n">
-        <v>7.55</v>
+        <v>4.99</v>
       </c>
       <c r="F12" t="n">
-        <v>16.3372</v>
+        <v>11.7565</v>
       </c>
       <c r="G12" t="n">
-        <v>14.71752</v>
+        <v>11.42792</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>19.2</v>
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
